--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575440623</v>
+        <v>46157.9311975087</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311975087</v>
+        <v>46157.93185677865</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185677865</v>
+        <v>46157.93406820405</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406820405</v>
+        <v>46157.93724932219</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724932219</v>
+        <v>46158.28222522043</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222522043</v>
+        <v>46158.29709063847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29709063847</v>
+        <v>46158.29822483591</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822483591</v>
+        <v>46158.3339346269</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339346269</v>
+        <v>46158.36863246619</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863246619</v>
+        <v>46158.37294221333</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
